--- a/artfynd/A 41391-2026 artfynd.xlsx
+++ b/artfynd/A 41391-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858015</v>
       </c>
       <c r="B2" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858016</v>
       </c>
       <c r="B3" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858017</v>
       </c>
       <c r="B4" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858018</v>
       </c>
       <c r="B5" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136858020</v>
       </c>
       <c r="B6" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>136858021</v>
       </c>
       <c r="B7" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136858022</v>
       </c>
       <c r="B8" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136858023</v>
       </c>
       <c r="B9" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>136857964</v>
       </c>
       <c r="B10" t="n">
-        <v>106488</v>
+        <v>106494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>136857965</v>
       </c>
       <c r="B11" t="n">
-        <v>106488</v>
+        <v>106494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41391-2026 artfynd.xlsx
+++ b/artfynd/A 41391-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858015</v>
       </c>
       <c r="B2" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858016</v>
       </c>
       <c r="B3" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858017</v>
       </c>
       <c r="B4" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858018</v>
       </c>
       <c r="B5" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136858020</v>
       </c>
       <c r="B6" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>136858021</v>
       </c>
       <c r="B7" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136858022</v>
       </c>
       <c r="B8" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136858023</v>
       </c>
       <c r="B9" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>136857964</v>
       </c>
       <c r="B10" t="n">
-        <v>106494</v>
+        <v>106498</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>136857965</v>
       </c>
       <c r="B11" t="n">
-        <v>106494</v>
+        <v>106498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41391-2026 artfynd.xlsx
+++ b/artfynd/A 41391-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858015</v>
       </c>
       <c r="B2" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858016</v>
       </c>
       <c r="B3" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858017</v>
       </c>
       <c r="B4" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858018</v>
       </c>
       <c r="B5" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136858020</v>
       </c>
       <c r="B6" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>136858021</v>
       </c>
       <c r="B7" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136858022</v>
       </c>
       <c r="B8" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136858023</v>
       </c>
       <c r="B9" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>136857964</v>
       </c>
       <c r="B10" t="n">
-        <v>106498</v>
+        <v>106500</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>136857965</v>
       </c>
       <c r="B11" t="n">
-        <v>106498</v>
+        <v>106500</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41391-2026 artfynd.xlsx
+++ b/artfynd/A 41391-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858015</v>
       </c>
       <c r="B2" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858016</v>
       </c>
       <c r="B3" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858017</v>
       </c>
       <c r="B4" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858018</v>
       </c>
       <c r="B5" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136858020</v>
       </c>
       <c r="B6" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>136858021</v>
       </c>
       <c r="B7" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136858022</v>
       </c>
       <c r="B8" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136858023</v>
       </c>
       <c r="B9" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>136857964</v>
       </c>
       <c r="B10" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>136857965</v>
       </c>
       <c r="B11" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41391-2026 artfynd.xlsx
+++ b/artfynd/A 41391-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858015</v>
       </c>
       <c r="B2" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858016</v>
       </c>
       <c r="B3" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858017</v>
       </c>
       <c r="B4" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858018</v>
       </c>
       <c r="B5" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136858020</v>
       </c>
       <c r="B6" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>136858021</v>
       </c>
       <c r="B7" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136858022</v>
       </c>
       <c r="B8" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136858023</v>
       </c>
       <c r="B9" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>136857964</v>
       </c>
       <c r="B10" t="n">
-        <v>106502</v>
+        <v>106515</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>136857965</v>
       </c>
       <c r="B11" t="n">
-        <v>106502</v>
+        <v>106515</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41391-2026 artfynd.xlsx
+++ b/artfynd/A 41391-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858015</v>
       </c>
       <c r="B2" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858016</v>
       </c>
       <c r="B3" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858017</v>
       </c>
       <c r="B4" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858018</v>
       </c>
       <c r="B5" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136858020</v>
       </c>
       <c r="B6" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>136858021</v>
       </c>
       <c r="B7" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136858022</v>
       </c>
       <c r="B8" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136858023</v>
       </c>
       <c r="B9" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>136857964</v>
       </c>
       <c r="B10" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>136857965</v>
       </c>
       <c r="B11" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41391-2026 artfynd.xlsx
+++ b/artfynd/A 41391-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858015</v>
       </c>
       <c r="B2" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858016</v>
       </c>
       <c r="B3" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858017</v>
       </c>
       <c r="B4" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858018</v>
       </c>
       <c r="B5" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136858020</v>
       </c>
       <c r="B6" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>136858021</v>
       </c>
       <c r="B7" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136858022</v>
       </c>
       <c r="B8" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136858023</v>
       </c>
       <c r="B9" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>136857964</v>
       </c>
       <c r="B10" t="n">
-        <v>106517</v>
+        <v>106521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>136857965</v>
       </c>
       <c r="B11" t="n">
-        <v>106517</v>
+        <v>106521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41391-2026 artfynd.xlsx
+++ b/artfynd/A 41391-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858015</v>
       </c>
       <c r="B2" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858016</v>
       </c>
       <c r="B3" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858017</v>
       </c>
       <c r="B4" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858018</v>
       </c>
       <c r="B5" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136858020</v>
       </c>
       <c r="B6" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>136858021</v>
       </c>
       <c r="B7" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136858022</v>
       </c>
       <c r="B8" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136858023</v>
       </c>
       <c r="B9" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>136857964</v>
       </c>
       <c r="B10" t="n">
-        <v>106521</v>
+        <v>106541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>136857965</v>
       </c>
       <c r="B11" t="n">
-        <v>106521</v>
+        <v>106541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41391-2026 artfynd.xlsx
+++ b/artfynd/A 41391-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858015</v>
       </c>
       <c r="B2" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858016</v>
       </c>
       <c r="B3" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858017</v>
       </c>
       <c r="B4" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858018</v>
       </c>
       <c r="B5" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136858020</v>
       </c>
       <c r="B6" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>136858021</v>
       </c>
       <c r="B7" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136858022</v>
       </c>
       <c r="B8" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136858023</v>
       </c>
       <c r="B9" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>136857964</v>
       </c>
       <c r="B10" t="n">
-        <v>106541</v>
+        <v>106542</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>136857965</v>
       </c>
       <c r="B11" t="n">
-        <v>106541</v>
+        <v>106542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41391-2026 artfynd.xlsx
+++ b/artfynd/A 41391-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858015</v>
       </c>
       <c r="B2" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858016</v>
       </c>
       <c r="B3" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858017</v>
       </c>
       <c r="B4" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858018</v>
       </c>
       <c r="B5" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136858020</v>
       </c>
       <c r="B6" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>136858021</v>
       </c>
       <c r="B7" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136858022</v>
       </c>
       <c r="B8" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136858023</v>
       </c>
       <c r="B9" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>136857964</v>
       </c>
       <c r="B10" t="n">
-        <v>106542</v>
+        <v>106547</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>136857965</v>
       </c>
       <c r="B11" t="n">
-        <v>106542</v>
+        <v>106547</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41391-2026 artfynd.xlsx
+++ b/artfynd/A 41391-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858015</v>
       </c>
       <c r="B2" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858016</v>
       </c>
       <c r="B3" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858017</v>
       </c>
       <c r="B4" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858018</v>
       </c>
       <c r="B5" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136858020</v>
       </c>
       <c r="B6" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>136858021</v>
       </c>
       <c r="B7" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136858022</v>
       </c>
       <c r="B8" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136858023</v>
       </c>
       <c r="B9" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>136857964</v>
       </c>
       <c r="B10" t="n">
-        <v>106547</v>
+        <v>106550</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>136857965</v>
       </c>
       <c r="B11" t="n">
-        <v>106547</v>
+        <v>106550</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41391-2026 artfynd.xlsx
+++ b/artfynd/A 41391-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858015</v>
       </c>
       <c r="B2" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858016</v>
       </c>
       <c r="B3" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858017</v>
       </c>
       <c r="B4" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858018</v>
       </c>
       <c r="B5" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136858020</v>
       </c>
       <c r="B6" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>136858021</v>
       </c>
       <c r="B7" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136858022</v>
       </c>
       <c r="B8" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136858023</v>
       </c>
       <c r="B9" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>136857964</v>
       </c>
       <c r="B10" t="n">
-        <v>106550</v>
+        <v>106556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>136857965</v>
       </c>
       <c r="B11" t="n">
-        <v>106550</v>
+        <v>106556</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41391-2026 artfynd.xlsx
+++ b/artfynd/A 41391-2026 artfynd.xlsx
@@ -1651,7 +1651,7 @@
         <v>136857964</v>
       </c>
       <c r="B10" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>136857965</v>
       </c>
       <c r="B11" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41391-2026 artfynd.xlsx
+++ b/artfynd/A 41391-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858015</v>
       </c>
       <c r="B2" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858016</v>
       </c>
       <c r="B3" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858017</v>
       </c>
       <c r="B4" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858018</v>
       </c>
       <c r="B5" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136858020</v>
       </c>
       <c r="B6" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>136858021</v>
       </c>
       <c r="B7" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>136858022</v>
       </c>
       <c r="B8" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136858023</v>
       </c>
       <c r="B9" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>136857964</v>
       </c>
       <c r="B10" t="n">
-        <v>106557</v>
+        <v>106569</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>136857965</v>
       </c>
       <c r="B11" t="n">
-        <v>106557</v>
+        <v>106569</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
